--- a/results/soae_T_xi [int 500ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
+++ b/results/soae_T_xi [int 500ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.0219362775065216</v>
+        <v>0.02192147244073282</v>
       </c>
       <c r="F2" t="n">
         <v>10.09595355218707</v>
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.01959660131309134</v>
+        <v>0.01959162465836898</v>
       </c>
       <c r="F3" t="n">
         <v>10.09595355218707</v>
@@ -589,7 +589,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.07249825028976278</v>
+        <v>0.07243667789395537</v>
       </c>
       <c r="F4" t="n">
         <v>3.09945385050024</v>
@@ -632,7 +632,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.0618436303307079</v>
+        <v>0.06171066842031853</v>
       </c>
       <c r="F5" t="n">
         <v>3.09945385050024</v>
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.2682456910254397</v>
+        <v>0.2680328010089406</v>
       </c>
       <c r="F6" t="n">
         <v>0.8253318426568844</v>
@@ -718,7 +718,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.2688052818430118</v>
+        <v>0.268673679847536</v>
       </c>
       <c r="F7" t="n">
         <v>0.8253318426568844</v>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0.1105146728464383</v>
+        <v>0.1105646707237456</v>
       </c>
       <c r="F8" t="n">
         <v>2.212581609474567</v>
@@ -804,7 +804,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.1090129335882332</v>
+        <v>0.1089233954828083</v>
       </c>
       <c r="F9" t="n">
         <v>2.212581609474567</v>
@@ -847,7 +847,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0.1105733551722878</v>
+        <v>0.1106477538303882</v>
       </c>
       <c r="F10" t="n">
         <v>1.306834054289299</v>
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>0.1291903356293772</v>
+        <v>0.1292192892892552</v>
       </c>
       <c r="F11" t="n">
         <v>1.306834054289299</v>
@@ -933,7 +933,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.3110023783231826</v>
+        <v>0.3109710385101812</v>
       </c>
       <c r="F12" t="n">
         <v>1.226981092761272</v>
@@ -976,7 +976,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.3138436165195568</v>
+        <v>0.313856957606763</v>
       </c>
       <c r="F13" t="n">
         <v>1.226981092761272</v>
@@ -1019,7 +1019,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.08217762391069885</v>
+        <v>0.08211898213611403</v>
       </c>
       <c r="F14" t="n">
         <v>2.396894500224019</v>
@@ -1062,7 +1062,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.07377941047392846</v>
+        <v>0.07349145369565069</v>
       </c>
       <c r="F15" t="n">
         <v>2.396894500224019</v>
@@ -1105,7 +1105,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.2006013451175047</v>
+        <v>0.200160335548025</v>
       </c>
       <c r="F16" t="n">
         <v>1.618801456042487</v>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.1794834959213314</v>
+        <v>0.1788802572899153</v>
       </c>
       <c r="F17" t="n">
         <v>1.618801456042487</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.3040211679242786</v>
+        <v>0.3041955429547736</v>
       </c>
       <c r="F18" t="n">
         <v>0.8820415846920716</v>
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.3231436217000073</v>
+        <v>0.323788504277897</v>
       </c>
       <c r="F19" t="n">
         <v>0.8820415846920716</v>
@@ -1277,7 +1277,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0825093742239754</v>
+        <v>0.08253564674998819</v>
       </c>
       <c r="F20" t="n">
         <v>2.415225068705968</v>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.08024934660966779</v>
+        <v>0.0800173145177555</v>
       </c>
       <c r="F21" t="n">
         <v>2.415225068705968</v>
@@ -1363,7 +1363,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.2461945503597759</v>
+        <v>0.2463178555350115</v>
       </c>
       <c r="F22" t="n">
         <v>1.281367686769816</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>0.2550686045868905</v>
+        <v>0.2551455735038457</v>
       </c>
       <c r="F23" t="n">
         <v>1.281367686769816</v>
@@ -1449,7 +1449,7 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0.02118622881149223</v>
+        <v>0.0211809124330134</v>
       </c>
       <c r="F24" t="n">
         <v>10.05992016213009</v>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>0.01891023636180317</v>
+        <v>0.01890915001738958</v>
       </c>
       <c r="F25" t="n">
         <v>10.05992016213009</v>
@@ -1535,7 +1535,7 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0.2300206528780061</v>
+        <v>0.2297600548860095</v>
       </c>
       <c r="F26" t="n">
         <v>0.8440441282866774</v>
@@ -1578,7 +1578,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.2496670920627559</v>
+        <v>0.2497034968736176</v>
       </c>
       <c r="F27" t="n">
         <v>0.8440441282866774</v>
@@ -1621,7 +1621,7 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.2904074713465594</v>
+        <v>0.2905260826491288</v>
       </c>
       <c r="F28" t="n">
         <v>1.254614652958397</v>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.3048894713052086</v>
+        <v>0.3051986513386781</v>
       </c>
       <c r="F29" t="n">
         <v>1.254614652958397</v>
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.05767607819617335</v>
+        <v>0.05776846155808335</v>
       </c>
       <c r="F30" t="n">
         <v>4.481984426888731</v>
@@ -1750,7 +1750,7 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.05047091711465247</v>
+        <v>0.0506597814653946</v>
       </c>
       <c r="F31" t="n">
         <v>4.481984426888731</v>
@@ -1793,7 +1793,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.08217752556021964</v>
+        <v>0.0820451535148814</v>
       </c>
       <c r="F32" t="n">
         <v>1.621707514273231</v>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.07536861852299405</v>
+        <v>0.07514052468399143</v>
       </c>
       <c r="F33" t="n">
         <v>1.621707514273231</v>
@@ -1879,7 +1879,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.02301064816076377</v>
+        <v>0.02295018884021304</v>
       </c>
       <c r="F34" t="n">
         <v>11.8803921636882</v>
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.02254020076318181</v>
+        <v>0.02249673752893688</v>
       </c>
       <c r="F35" t="n">
         <v>11.8803921636882</v>
@@ -1965,7 +1965,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.00756456687256829</v>
+        <v>0.007556608399069091</v>
       </c>
       <c r="F36" t="n">
         <v>40.81661019133534</v>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.006808877730972335</v>
+        <v>0.006813560539809738</v>
       </c>
       <c r="F37" t="n">
         <v>40.81661019133534</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>0.01646774498548158</v>
+        <v>0.01645515839051331</v>
       </c>
       <c r="F38" t="n">
         <v>19.05817478384657</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>0.0162258685228197</v>
+        <v>0.01621827296848035</v>
       </c>
       <c r="F39" t="n">
         <v>19.05817478384657</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>0.009203663679918679</v>
+        <v>0.009203479573320376</v>
       </c>
       <c r="F40" t="n">
         <v>33.25889734469793</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>0.008476699974057171</v>
+        <v>0.008487549100613376</v>
       </c>
       <c r="F41" t="n">
         <v>33.25889734469793</v>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>0.01671290659416064</v>
+        <v>0.0166912674894345</v>
       </c>
       <c r="F42" t="n">
         <v>16.38970637248534</v>
@@ -2266,7 +2266,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>0.01576028292178362</v>
+        <v>0.01575351397592169</v>
       </c>
       <c r="F43" t="n">
         <v>16.38970637248534</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0.00926886434778286</v>
+        <v>0.00927583827701009</v>
       </c>
       <c r="F44" t="n">
         <v>30.52335899097242</v>
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>0.008218086599018471</v>
+        <v>0.008227504107781572</v>
       </c>
       <c r="F45" t="n">
         <v>30.52335899097242</v>
@@ -2395,7 +2395,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>0.01305462519161128</v>
+        <v>0.01308347798524461</v>
       </c>
       <c r="F46" t="n">
         <v>24.19350636189434</v>
@@ -2438,7 +2438,7 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>0.01284391080912472</v>
+        <v>0.01287800929518558</v>
       </c>
       <c r="F47" t="n">
         <v>24.19350636189434</v>
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>0.008168304292153804</v>
+        <v>0.00815345212757485</v>
       </c>
       <c r="F48" t="n">
         <v>42.70877068563502</v>
@@ -2524,7 +2524,7 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>0.007816297937344797</v>
+        <v>0.007808042579072151</v>
       </c>
       <c r="F49" t="n">
         <v>42.70877068563502</v>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.01234210343926255</v>
+        <v>0.01234549493159653</v>
       </c>
       <c r="F50" t="n">
         <v>22.02734034403161</v>
@@ -2610,7 +2610,7 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.01098986966355024</v>
+        <v>0.01101170588009591</v>
       </c>
       <c r="F51" t="n">
         <v>22.02734034403161</v>
@@ -2653,7 +2653,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.0201082647637037</v>
+        <v>0.02008935749007648</v>
       </c>
       <c r="F52" t="n">
         <v>14.68264699299626</v>
@@ -2696,7 +2696,7 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.01949535541871019</v>
+        <v>0.01949270403359805</v>
       </c>
       <c r="F53" t="n">
         <v>14.68264699299626</v>
@@ -2739,7 +2739,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.01211016847313676</v>
+        <v>0.01208808364777014</v>
       </c>
       <c r="F54" t="n">
         <v>26.1281172770193</v>
@@ -2782,7 +2782,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.01242930971136674</v>
+        <v>0.01242356113981088</v>
       </c>
       <c r="F55" t="n">
         <v>26.1281172770193</v>
@@ -2825,7 +2825,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.01273490785446807</v>
+        <v>0.01277772435025441</v>
       </c>
       <c r="F56" t="n">
         <v>24.43832250664904</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.01258882029704509</v>
+        <v>0.01265791068458004</v>
       </c>
       <c r="F57" t="n">
         <v>24.43832250664904</v>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.01371279735082223</v>
+        <v>0.01368194137753805</v>
       </c>
       <c r="F58" t="n">
         <v>25.14257025564731</v>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.01262681385931631</v>
+        <v>0.01261840299631687</v>
       </c>
       <c r="F59" t="n">
         <v>25.14257025564731</v>
@@ -2997,7 +2997,7 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.005853506179688073</v>
+        <v>0.005844085012140725</v>
       </c>
       <c r="F60" t="n">
         <v>64.87424396895483</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.005233560101993614</v>
+        <v>0.005236572434296271</v>
       </c>
       <c r="F61" t="n">
         <v>64.87424396895483</v>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.006867980041989881</v>
+        <v>0.006861612053912363</v>
       </c>
       <c r="F62" t="n">
         <v>48.24737092155696</v>
@@ -3126,7 +3126,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.006025987003475348</v>
+        <v>0.006030410043182355</v>
       </c>
       <c r="F63" t="n">
         <v>48.24737092155696</v>
@@ -3169,7 +3169,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.00695219917239725</v>
+        <v>0.006957489404157989</v>
       </c>
       <c r="F64" t="n">
         <v>42.07107102770869</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.00628398759851471</v>
+        <v>0.00630878068157874</v>
       </c>
       <c r="F65" t="n">
         <v>42.07107102770869</v>
@@ -3255,7 +3255,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>0.007601992073759025</v>
+        <v>0.00759196108831005</v>
       </c>
       <c r="F66" t="n">
         <v>40.32418949488441</v>
@@ -3298,7 +3298,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>0.00693081861182945</v>
+        <v>0.006944766465627028</v>
       </c>
       <c r="F67" t="n">
         <v>40.32418949488441</v>
@@ -3341,7 +3341,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>0.01255378224642605</v>
+        <v>0.01253956501288159</v>
       </c>
       <c r="F68" t="n">
         <v>21.79457757467633</v>
@@ -3384,7 +3384,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>0.01169654357533647</v>
+        <v>0.01171141101023465</v>
       </c>
       <c r="F69" t="n">
         <v>21.79457757467633</v>
@@ -3427,7 +3427,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>0.008054229382686393</v>
+        <v>0.008053351503928002</v>
       </c>
       <c r="F70" t="n">
         <v>35.27900051644691</v>
@@ -3470,7 +3470,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>0.007220203032733018</v>
+        <v>0.007226595953644211</v>
       </c>
       <c r="F71" t="n">
         <v>35.27900051644691</v>
@@ -3513,7 +3513,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>0.0164314718380737</v>
+        <v>0.01642771343067338</v>
       </c>
       <c r="F72" t="n">
         <v>15.48239598695274</v>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>0.01648802183019945</v>
+        <v>0.01650255846565633</v>
       </c>
       <c r="F73" t="n">
         <v>15.48239598695274</v>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>0.01052957606388653</v>
+        <v>0.01052564546097794</v>
       </c>
       <c r="F74" t="n">
         <v>26.01227642789845</v>
@@ -3642,7 +3642,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>0.009083446587361198</v>
+        <v>0.009105281354875101</v>
       </c>
       <c r="F75" t="n">
         <v>26.01227642789845</v>
@@ -3685,7 +3685,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>0.01018300460773422</v>
+        <v>0.01019150786156407</v>
       </c>
       <c r="F76" t="n">
         <v>24.55723338600139</v>
@@ -3728,7 +3728,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>0.009421556538132651</v>
+        <v>0.009432896882832574</v>
       </c>
       <c r="F77" t="n">
         <v>24.55723338600139</v>
@@ -3771,7 +3771,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>0.01262586536945309</v>
+        <v>0.01265128056363023</v>
       </c>
       <c r="F78" t="n">
         <v>23.555089386247</v>
@@ -3814,7 +3814,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>0.01200301531426012</v>
+        <v>0.01201148984059485</v>
       </c>
       <c r="F79" t="n">
         <v>23.555089386247</v>
@@ -3857,7 +3857,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>0.00893094504640644</v>
+        <v>0.008919939446705471</v>
       </c>
       <c r="F80" t="n">
         <v>30.94992821931555</v>
@@ -3900,7 +3900,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>0.008158186404323232</v>
+        <v>0.008161633652188367</v>
       </c>
       <c r="F81" t="n">
         <v>30.94992821931555</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>0.01515192852236255</v>
+        <v>0.01514262148641145</v>
       </c>
       <c r="F82" t="n">
         <v>17.11041974211544</v>
@@ -3986,7 +3986,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>0.01390292328145756</v>
+        <v>0.01389970624590156</v>
       </c>
       <c r="F83" t="n">
         <v>17.11041974211544</v>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>0.01015594947391362</v>
+        <v>0.01016285511686901</v>
       </c>
       <c r="F84" t="n">
         <v>25.09099671696914</v>
@@ -4072,7 +4072,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>0.008994970880494427</v>
+        <v>0.00902963637245153</v>
       </c>
       <c r="F85" t="n">
         <v>25.09099671696914</v>
@@ -4115,7 +4115,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>0.006155011955754493</v>
+        <v>0.006160572615730648</v>
       </c>
       <c r="F86" t="n">
         <v>56.10647072185828</v>
@@ -4158,7 +4158,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>0.005485573004534722</v>
+        <v>0.005496502582419299</v>
       </c>
       <c r="F87" t="n">
         <v>56.10647072185828</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>0.0121783681688674</v>
+        <v>0.01217778072012911</v>
       </c>
       <c r="F88" t="n">
         <v>26.61131083407046</v>
@@ -4244,7 +4244,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>0.01163367888296346</v>
+        <v>0.01164333414178339</v>
       </c>
       <c r="F89" t="n">
         <v>26.61131083407046</v>
@@ -4287,7 +4287,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>0.01470761424296082</v>
+        <v>0.01473577106937144</v>
       </c>
       <c r="F90" t="n">
         <v>17.17910082644781</v>
@@ -4330,7 +4330,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>0.01436170366684906</v>
+        <v>0.01436758159420198</v>
       </c>
       <c r="F91" t="n">
         <v>17.17910082644781</v>
@@ -4373,7 +4373,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>0.007622521823974839</v>
+        <v>0.007628807129093314</v>
       </c>
       <c r="F92" t="n">
         <v>41.33077231855378</v>
@@ -4416,7 +4416,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>0.006820761241148247</v>
+        <v>0.006833533258403254</v>
       </c>
       <c r="F93" t="n">
         <v>41.33077231855378</v>
@@ -4459,7 +4459,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>0.008712946006938964</v>
+        <v>0.008689749638384986</v>
       </c>
       <c r="F94" t="n">
         <v>31.93359446629537</v>
@@ -4502,7 +4502,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>0.007707570331724818</v>
+        <v>0.007695466723931167</v>
       </c>
       <c r="F95" t="n">
         <v>31.93359446629537</v>
@@ -4545,7 +4545,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.009299271297917253</v>
+        <v>0.009303635548717175</v>
       </c>
       <c r="F96" t="n">
         <v>35.1035288170361</v>
@@ -4588,7 +4588,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>0.008422181199917472</v>
+        <v>0.00841582860100655</v>
       </c>
       <c r="F97" t="n">
         <v>35.1035288170361</v>
@@ -4631,7 +4631,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>0.005108639841650837</v>
+        <v>0.005100236408357663</v>
       </c>
       <c r="F98" t="n">
         <v>70.42713629849885</v>
@@ -4674,7 +4674,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>0.004428480988994314</v>
+        <v>0.004431242619417812</v>
       </c>
       <c r="F99" t="n">
         <v>70.42713629849885</v>
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>0.006397867208683139</v>
+        <v>0.006406191200672658</v>
       </c>
       <c r="F100" t="n">
         <v>48.09727907943265</v>
@@ -4760,7 +4760,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>0.00572532109142596</v>
+        <v>0.005740326326695206</v>
       </c>
       <c r="F101" t="n">
         <v>48.09727907943265</v>
@@ -4803,7 +4803,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>0.006657229858262662</v>
+        <v>0.006658158281561873</v>
       </c>
       <c r="F102" t="n">
         <v>48.35560222806118</v>
@@ -4846,7 +4846,7 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>0.005869986425519522</v>
+        <v>0.005869987979061153</v>
       </c>
       <c r="F103" t="n">
         <v>48.35560222806118</v>
@@ -4889,7 +4889,7 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>0.008075088689307395</v>
+        <v>0.008096479184514739</v>
       </c>
       <c r="F104" t="n">
         <v>41.34715232351992</v>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>0.007257727510290389</v>
+        <v>0.007278279341248796</v>
       </c>
       <c r="F105" t="n">
         <v>41.34715232351992</v>
@@ -4975,7 +4975,7 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>0.006457699524517901</v>
+        <v>0.006453809587529244</v>
       </c>
       <c r="F106" t="n">
         <v>48.82276869525922</v>
@@ -5018,7 +5018,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>0.005668019022775288</v>
+        <v>0.00567863861071301</v>
       </c>
       <c r="F107" t="n">
         <v>48.82276869525922</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>0.00826646399055125</v>
+        <v>0.008262336950781105</v>
       </c>
       <c r="F108" t="n">
         <v>34.72295925128499</v>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>0.00721430792667434</v>
+        <v>0.007228154312042025</v>
       </c>
       <c r="F109" t="n">
         <v>34.72295925128499</v>
@@ -5147,7 +5147,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>0.008094127045788111</v>
+        <v>0.0080854022945194</v>
       </c>
       <c r="F110" t="n">
         <v>43.26334017048392</v>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>0.007355109494497121</v>
+        <v>0.007360767935563276</v>
       </c>
       <c r="F111" t="n">
         <v>43.26334017048392</v>
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>0.004313593324436761</v>
+        <v>0.004307083579041558</v>
       </c>
       <c r="F112" t="n">
         <v>91.05438059951148</v>
@@ -5276,7 +5276,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>0.003853124516805728</v>
+        <v>0.003853320281095354</v>
       </c>
       <c r="F113" t="n">
         <v>91.05438059951148</v>
@@ -5319,7 +5319,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.01015438512298335</v>
+        <v>0.01012326872159529</v>
       </c>
       <c r="F114" t="n">
         <v>29.15344518718943</v>
@@ -5362,7 +5362,7 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>0.00873094513805427</v>
+        <v>0.008731877362000007</v>
       </c>
       <c r="F115" t="n">
         <v>29.15344518718943</v>
@@ -5405,7 +5405,7 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>0.006997876959606876</v>
+        <v>0.007020917784861589</v>
       </c>
       <c r="F116" t="n">
         <v>49.72373786348046</v>
@@ -5448,7 +5448,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>0.00617499534862222</v>
+        <v>0.006187452161933379</v>
       </c>
       <c r="F117" t="n">
         <v>49.72373786348046</v>
@@ -5491,7 +5491,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.01637045162195413</v>
+        <v>0.01635776688598447</v>
       </c>
       <c r="F118" t="n">
         <v>19.85800760568668</v>
@@ -5534,7 +5534,7 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>0.01497278591766005</v>
+        <v>0.01499113432822056</v>
       </c>
       <c r="F119" t="n">
         <v>19.85800760568668</v>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>0.007118531833044538</v>
+        <v>0.007115128334952403</v>
       </c>
       <c r="F120" t="n">
         <v>44.79676977747089</v>
@@ -5620,7 +5620,7 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>0.006383257120243808</v>
+        <v>0.006384527909238303</v>
       </c>
       <c r="F121" t="n">
         <v>44.79676977747089</v>
@@ -5663,7 +5663,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>0.004440725470667249</v>
+        <v>0.004438828407991317</v>
       </c>
       <c r="F122" t="n">
         <v>86.85132295553052</v>
@@ -5706,7 +5706,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>0.003886156541388321</v>
+        <v>0.003896773702617103</v>
       </c>
       <c r="F123" t="n">
         <v>86.85132295553052</v>
@@ -5749,7 +5749,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>0.0554009617302032</v>
+        <v>0.05544972170588747</v>
       </c>
       <c r="F124" t="n">
         <v>5.437958953595492</v>
@@ -5792,7 +5792,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>0.05186416506140334</v>
+        <v>0.0519469016198635</v>
       </c>
       <c r="F125" t="n">
         <v>5.437958953595492</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>0.006737053183372243</v>
+        <v>0.006729421628324178</v>
       </c>
       <c r="F126" t="n">
         <v>47.57406740201719</v>
@@ -5878,7 +5878,7 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>0.005927930854009116</v>
+        <v>0.005940542933346704</v>
       </c>
       <c r="F127" t="n">
         <v>47.57406740201719</v>
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.02500220837685947</v>
+        <v>0.02496259104148581</v>
       </c>
       <c r="F128" t="n">
         <v>11.3439055252793</v>
@@ -5964,7 +5964,7 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>0.02412769696466165</v>
+        <v>0.02412440278292536</v>
       </c>
       <c r="F129" t="n">
         <v>11.3439055252793</v>

--- a/results/soae_T_xi [int 500ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
+++ b/results/soae_T_xi [int 500ms, bw=10p max, kaiser, df=50hz, rip=100db, crop=200hz, tau=500ms, hop_psd=250ms, nfft=None, win=hann].xlsx
@@ -499,7 +499,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -585,7 +585,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -671,7 +671,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -757,7 +757,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -843,7 +843,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -929,7 +929,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -1445,7 +1445,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -1703,7 +1703,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -2047,7 +2047,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -2133,7 +2133,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -2219,7 +2219,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2305,7 +2305,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2477,7 +2477,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2649,7 +2649,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -3509,7 +3509,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -3853,7 +3853,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -4283,7 +4283,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E92" t="n">
@@ -4455,7 +4455,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E94" t="n">
@@ -4541,7 +4541,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E96" t="n">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E98" t="n">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E100" t="n">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E102" t="n">
@@ -4885,7 +4885,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E106" t="n">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E108" t="n">
@@ -5143,7 +5143,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -5315,7 +5315,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E114" t="n">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E116" t="n">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E118" t="n">
@@ -5573,7 +5573,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -5745,7 +5745,7 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E124" t="n">
@@ -5831,7 +5831,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>W</t>
         </is>
       </c>
       <c r="E128" t="n">
